--- a/信效度检验结果.xlsx
+++ b/信效度检验结果.xlsx
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,52 +419,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>构念</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>α</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AVE</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>CITC_1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>载荷_1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>CITC_2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>载荷_2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>CITC_3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>载荷_3</t>
         </is>
@@ -489,31 +477,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.911</v>
       </c>
       <c r="C2" t="n">
-        <v>0.958</v>
+        <v>0.948</v>
       </c>
       <c r="D2" t="n">
-        <v>0.885</v>
+        <v>0.858</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9</v>
+        <v>0.783</v>
       </c>
       <c r="F2" t="n">
-        <v>0.958</v>
+        <v>0.847</v>
       </c>
       <c r="G2" t="n">
-        <v>0.863</v>
+        <v>0.873</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.956</v>
       </c>
       <c r="I2" t="n">
-        <v>0.833</v>
+        <v>0.896</v>
       </c>
       <c r="J2" t="n">
-        <v>0.924</v>
+        <v>0.971</v>
       </c>
     </row>
     <row r="3">
@@ -523,31 +511,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.832</v>
+        <v>0.972</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9</v>
+        <v>0.984</v>
       </c>
       <c r="D3" t="n">
-        <v>0.749</v>
+        <v>0.953</v>
       </c>
       <c r="E3" t="n">
-        <v>0.677</v>
+        <v>0.927</v>
       </c>
       <c r="F3" t="n">
-        <v>0.856</v>
+        <v>0.957</v>
       </c>
       <c r="G3" t="n">
-        <v>0.676</v>
+        <v>0.979</v>
       </c>
       <c r="H3" t="n">
-        <v>0.856</v>
+        <v>0.992</v>
       </c>
       <c r="I3" t="n">
-        <v>0.724</v>
+        <v>0.947</v>
       </c>
       <c r="J3" t="n">
-        <v>0.884</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="4">
@@ -557,31 +545,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.854</v>
+        <v>0.879</v>
       </c>
       <c r="C4" t="n">
-        <v>0.912</v>
+        <v>0.928</v>
       </c>
       <c r="D4" t="n">
-        <v>0.776</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.722</v>
+        <v>0.766</v>
       </c>
       <c r="F4" t="n">
-        <v>0.879</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.749</v>
+        <v>0.845</v>
       </c>
       <c r="H4" t="n">
-        <v>0.893</v>
+        <v>0.924</v>
       </c>
       <c r="I4" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="J4" t="n">
-        <v>0.871</v>
+        <v>0.832</v>
       </c>
     </row>
     <row r="5">
@@ -591,65 +579,65 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.848</v>
+        <v>0.771</v>
       </c>
       <c r="C5" t="n">
-        <v>0.908</v>
+        <v>0.875</v>
       </c>
       <c r="D5" t="n">
-        <v>0.767</v>
+        <v>0.7</v>
       </c>
       <c r="E5" t="n">
-        <v>0.672</v>
+        <v>0.769</v>
       </c>
       <c r="F5" t="n">
-        <v>0.849</v>
+        <v>0.845</v>
       </c>
       <c r="G5" t="n">
-        <v>0.747</v>
+        <v>0.769</v>
       </c>
       <c r="H5" t="n">
-        <v>0.894</v>
+        <v>0.845</v>
       </c>
       <c r="I5" t="n">
-        <v>0.728</v>
+        <v>0.388</v>
       </c>
       <c r="J5" t="n">
-        <v>0.884</v>
+        <v>0.821</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GBI（群体归属感）</t>
+          <t>GBI（群体归属认同）</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.839</v>
+        <v>0.879</v>
       </c>
       <c r="C6" t="n">
-        <v>0.904</v>
+        <v>0.944</v>
       </c>
       <c r="D6" t="n">
-        <v>0.757</v>
+        <v>0.848</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.835</v>
       </c>
       <c r="F6" t="n">
-        <v>0.862</v>
+        <v>0.883</v>
       </c>
       <c r="G6" t="n">
-        <v>0.708</v>
+        <v>0.859</v>
       </c>
       <c r="H6" t="n">
-        <v>0.874</v>
+        <v>0.983</v>
       </c>
       <c r="I6" t="n">
-        <v>0.71</v>
+        <v>0.853</v>
       </c>
       <c r="J6" t="n">
-        <v>0.875</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="7">
@@ -659,28 +647,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.856</v>
+        <v>0.921</v>
       </c>
       <c r="C7" t="n">
-        <v>0.913</v>
+        <v>0.954</v>
       </c>
       <c r="D7" t="n">
-        <v>0.777</v>
+        <v>0.874</v>
       </c>
       <c r="E7" t="n">
-        <v>0.744</v>
+        <v>0.922</v>
       </c>
       <c r="F7" t="n">
-        <v>0.89</v>
+        <v>0.965</v>
       </c>
       <c r="G7" t="n">
-        <v>0.727</v>
+        <v>0.855</v>
       </c>
       <c r="H7" t="n">
-        <v>0.88</v>
+        <v>0.962</v>
       </c>
       <c r="I7" t="n">
-        <v>0.718</v>
+        <v>0.819</v>
       </c>
       <c r="J7" t="n">
         <v>0.875</v>
@@ -693,31 +681,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.863</v>
+        <v>0.877</v>
       </c>
       <c r="C8" t="n">
-        <v>0.917</v>
+        <v>0.925</v>
       </c>
       <c r="D8" t="n">
-        <v>0.786</v>
+        <v>0.804</v>
       </c>
       <c r="E8" t="n">
-        <v>0.743</v>
+        <v>0.732</v>
       </c>
       <c r="F8" t="n">
-        <v>0.888</v>
+        <v>0.89</v>
       </c>
       <c r="G8" t="n">
-        <v>0.759</v>
+        <v>0.79</v>
       </c>
       <c r="H8" t="n">
-        <v>0.897</v>
+        <v>0.919</v>
       </c>
       <c r="I8" t="n">
-        <v>0.72</v>
+        <v>0.776</v>
       </c>
       <c r="J8" t="n">
-        <v>0.874</v>
+        <v>0.881</v>
       </c>
     </row>
     <row r="9">
@@ -727,65 +715,65 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="C9" t="n">
-        <v>0.92</v>
+        <v>0.957</v>
       </c>
       <c r="D9" t="n">
-        <v>0.794</v>
+        <v>0.88</v>
       </c>
       <c r="E9" t="n">
-        <v>0.738</v>
+        <v>0.905</v>
       </c>
       <c r="F9" t="n">
-        <v>0.883</v>
+        <v>0.955</v>
       </c>
       <c r="G9" t="n">
-        <v>0.756</v>
+        <v>0.893</v>
       </c>
       <c r="H9" t="n">
-        <v>0.894</v>
+        <v>0.959</v>
       </c>
       <c r="I9" t="n">
-        <v>0.76</v>
+        <v>0.782</v>
       </c>
       <c r="J9" t="n">
-        <v>0.896</v>
+        <v>0.899</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TWI（旅游消费意愿）</t>
+          <t>TWI（旅游/消费延伸意愿）</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.843</v>
+        <v>0.774</v>
       </c>
       <c r="C10" t="n">
-        <v>0.905</v>
+        <v>0.865</v>
       </c>
       <c r="D10" t="n">
-        <v>0.761</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>0.732</v>
+        <v>0.516</v>
       </c>
       <c r="F10" t="n">
-        <v>0.886</v>
+        <v>0.668</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.716</v>
       </c>
       <c r="H10" t="n">
-        <v>0.86</v>
+        <v>0.845</v>
       </c>
       <c r="I10" t="n">
-        <v>0.706</v>
+        <v>0.667</v>
       </c>
       <c r="J10" t="n">
-        <v>0.871</v>
+        <v>0.946</v>
       </c>
     </row>
   </sheetData>
@@ -803,47 +791,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>构念</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>SMI</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PSR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>CTA</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>EEM</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>GBI</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>RSA</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>PVI</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>TWI</t>
         </is>
@@ -857,7 +845,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[0.941]</t>
+          <t>[0.926]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -875,11 +863,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.902</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[0.866]</t>
+          <t>[0.976]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -896,14 +884,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.86</v>
+        <v>0.245</v>
       </c>
       <c r="C4" t="n">
-        <v>0.839</v>
+        <v>0.146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[0.881]</t>
+          <t>[0.900]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -919,17 +907,17 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.865</v>
+        <v>0.498</v>
       </c>
       <c r="C5" t="n">
-        <v>0.834</v>
+        <v>0.536</v>
       </c>
       <c r="D5" t="n">
-        <v>0.801</v>
+        <v>0.177</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[0.876]</t>
+          <t>[0.837]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -944,20 +932,20 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.895</v>
+        <v>0.875</v>
       </c>
       <c r="C6" t="n">
-        <v>0.855</v>
+        <v>0.837</v>
       </c>
       <c r="D6" t="n">
-        <v>0.824</v>
+        <v>0.253</v>
       </c>
       <c r="E6" t="n">
-        <v>0.852</v>
+        <v>0.461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[0.870]</t>
+          <t>[0.921]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -971,23 +959,23 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.902</v>
+        <v>0.914</v>
       </c>
       <c r="C7" t="n">
-        <v>0.863</v>
+        <v>0.851</v>
       </c>
       <c r="D7" t="n">
-        <v>0.848</v>
+        <v>0.331</v>
       </c>
       <c r="E7" t="n">
-        <v>0.828</v>
+        <v>0.419</v>
       </c>
       <c r="F7" t="n">
-        <v>0.869</v>
+        <v>0.904</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[0.882]</t>
+          <t>[0.935]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1000,26 +988,26 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.896</v>
+        <v>0.866</v>
       </c>
       <c r="C8" t="n">
-        <v>0.875</v>
+        <v>0.837</v>
       </c>
       <c r="D8" t="n">
-        <v>0.87</v>
+        <v>0.372</v>
       </c>
       <c r="E8" t="n">
-        <v>0.849</v>
+        <v>0.59</v>
       </c>
       <c r="F8" t="n">
-        <v>0.871</v>
+        <v>0.829</v>
       </c>
       <c r="G8" t="n">
-        <v>0.871</v>
+        <v>0.86</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[0.891]</t>
+          <t>[0.938]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1031,29 +1019,29 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.859</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>0.859</v>
+        <v>0.506</v>
       </c>
       <c r="D9" t="n">
-        <v>0.839</v>
+        <v>0.584</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.304</v>
       </c>
       <c r="F9" t="n">
-        <v>0.858</v>
+        <v>0.481</v>
       </c>
       <c r="G9" t="n">
-        <v>0.824</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.876</v>
+        <v>0.61</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[0.872]</t>
+          <t>[0.827]</t>
         </is>
       </c>
     </row>
@@ -1072,37 +1060,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>构念</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>EEM</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>GBI</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>RSA</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>PCB</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>PVI</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>TWI</t>
         </is>
@@ -1116,7 +1104,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[0.876]</t>
+          <t>[0.837]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -1132,11 +1120,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.852</v>
+        <v>0.461</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[0.870]</t>
+          <t>[0.921]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -1151,14 +1139,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.828</v>
+        <v>0.419</v>
       </c>
       <c r="C4" t="n">
-        <v>0.869</v>
+        <v>0.904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[0.882]</t>
+          <t>[0.935]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -1172,17 +1160,17 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.803</v>
+        <v>-0.294</v>
       </c>
       <c r="C5" t="n">
-        <v>0.834</v>
+        <v>-0.472</v>
       </c>
       <c r="D5" t="n">
-        <v>0.842</v>
+        <v>-0.549</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[0.886]</t>
+          <t>[0.897]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -1195,20 +1183,20 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.849</v>
+        <v>0.59</v>
       </c>
       <c r="C6" t="n">
-        <v>0.871</v>
+        <v>0.829</v>
       </c>
       <c r="D6" t="n">
-        <v>0.871</v>
+        <v>0.86</v>
       </c>
       <c r="E6" t="n">
-        <v>0.86</v>
+        <v>-0.611</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[0.891]</t>
+          <t>[0.938]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1220,23 +1208,23 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.304</v>
       </c>
       <c r="C7" t="n">
-        <v>0.858</v>
+        <v>0.481</v>
       </c>
       <c r="D7" t="n">
-        <v>0.824</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8110000000000001</v>
+        <v>-0.77</v>
       </c>
       <c r="F7" t="n">
-        <v>0.876</v>
+        <v>0.61</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[0.872]</t>
+          <t>[0.827]</t>
         </is>
       </c>
     </row>
